--- a/중복출고_분석결과.xlsx
+++ b/중복출고_분석결과.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전체_요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="★과잉출고_요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="★과잉출고_상세행" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cigro없음_요약" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cigro없음_상세행" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="수량일치_중복_요약" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="수량일치_중복_상세행" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체_요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="★과잉출고_요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="★과잉출고_상세행" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cigro없음_요약" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cigro없음_상세행" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수량일치_중복_요약" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수량일치_중복_상세행" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,37 +435,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -2687,37 +2699,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -2927,242 +2939,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>고객명</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>출고일자</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>출고상태</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>운송장번호</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>매출처</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>UserId</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>작업일자</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>작업번호</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>출고번호</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>박스입수량</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>박스환산수량</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>잔여수량</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>핸드폰번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>받는자주소</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>참고사항</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>주문기재사항</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>배송기재사항</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>세부참고사항</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>입력자</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>입력시간</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>수정자</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>수정시간</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>주문자명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>유효일자</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>온라인주문번호</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>의뢰일자</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>의뢰번호</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>박스수량</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>포장구분</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>WHCD</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>매핑명</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>의뢰구분</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>판매금액</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>옵션명</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>택배사</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
@@ -6569,37 +6581,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -7402,242 +7414,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>고객명</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>출고일자</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>출고상태</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>운송장번호</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>매출처</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>UserId</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>작업일자</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>작업번호</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>출고번호</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>박스입수량</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>박스환산수량</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>잔여수량</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>핸드폰번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>받는자주소</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>참고사항</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>주문기재사항</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>배송기재사항</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>세부참고사항</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>입력자</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>입력시간</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>수정자</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>수정시간</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>주문자명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>유효일자</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>온라인주문번호</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>의뢰일자</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>의뢰번호</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>박스수량</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>포장구분</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>WHCD</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>매핑명</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>의뢰구분</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>판매금액</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>옵션명</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>택배사</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
@@ -25676,37 +25688,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -26969,242 +26981,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>고객명</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>출고일자</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>출고상태</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>운송장번호</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>매출처</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>UserId</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>작업일자</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>작업번호</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>출고번호</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>박스입수량</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>박스환산수량</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>잔여수량</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>핸드폰번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>받는자주소</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>참고사항</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>주문기재사항</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>배송기재사항</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>세부참고사항</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>입력자</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>입력시간</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>수정자</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>수정시간</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>주문자명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>유효일자</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>온라인주문번호</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>의뢰일자</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>의뢰번호</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>박스수량</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>포장구분</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>WHCD</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>매핑명</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>의뢰구분</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>판매금액</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>옵션명</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>택배사</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>

--- a/중복출고_분석결과.xlsx
+++ b/중복출고_분석결과.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전체_요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="★과잉출고_요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="★과잉출고_상세행" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cigro없음_요약" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="부족출고_요약" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="부족출고_상세행" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cigro없음_상세행" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="수량일치_중복_요약" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="수량일치_중복_상세행" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체_요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="★과잉출고_요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="★과잉출고_상세행" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cigro없음_요약" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부족출고_요약" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부족출고_상세행" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cigro없음_상세행" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수량일치_중복_요약" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수량일치_중복_상세행" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,52 +437,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>채널</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>키유형</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -1621,52 +1633,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>채널</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>키유형</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -1687,242 +1699,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>매출처</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>고객명</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>출고일자</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>출고상태</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>운송장번호</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>UserId</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>작업일자</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>작업번호</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>출고번호</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>박스입수량</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>박스환산수량</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>잔여수량</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>핸드폰번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>받는자주소</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>참고사항</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>주문기재사항</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>배송기재사항</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>세부참고사항</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>입력자</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>입력시간</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>수정자</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>수정시간</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>주문자명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>유효일자</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>온라인주문번호</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>의뢰일자</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>의뢰번호</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>박스수량</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>포장구분</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>WHCD</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>매핑명</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>의뢰구분</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>판매금액</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>옵션명</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>택배사</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
@@ -1943,52 +1955,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>채널</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>키유형</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -2593,52 +2605,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>채널</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>키유형</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -2701,242 +2713,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>매출처</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>고객명</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>출고일자</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>출고상태</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>운송장번호</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>UserId</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>작업일자</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>작업번호</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>출고번호</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>박스입수량</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>박스환산수량</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>잔여수량</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>핸드폰번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>받는자주소</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>참고사항</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>주문기재사항</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>배송기재사항</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>세부참고사항</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>입력자</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>입력시간</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>수정자</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>수정시간</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>주문자명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>유효일자</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>온라인주문번호</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>의뢰일자</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>의뢰번호</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>박스수량</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>포장구분</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>WHCD</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>매핑명</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>의뢰구분</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>판매금액</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>옵션명</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>택배사</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
@@ -3401,242 +3413,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>매출처</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>고객명</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>출고일자</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>출고상태</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>운송장번호</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>UserId</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>작업일자</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>작업번호</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>출고번호</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>박스입수량</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>박스환산수량</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>잔여수량</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>핸드폰번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>받는자주소</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>참고사항</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>주문기재사항</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>배송기재사항</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>세부참고사항</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>입력자</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>입력시간</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>수정자</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>수정시간</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>주문자명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>유효일자</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>온라인주문번호</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>의뢰일자</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>의뢰번호</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>박스수량</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>포장구분</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>WHCD</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>매핑명</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>의뢰구분</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>판매금액</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>옵션명</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>택배사</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
@@ -13245,52 +13257,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>채널</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>키유형</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>WMS_출고횟수</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>WMS_총수량</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cigro_존재</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cigro_수량</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>수량차이_WMS합산빼기Cigro</t>
         </is>
@@ -13815,242 +13827,242 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>매출처</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>주문번호</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>부주문코드</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>상품코드</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>상품명</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>고객명</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>출고일자</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>출고상태</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>운송장번호</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>UserId</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>작업일자</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>작업번호</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>출고번호</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>브랜드</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>박스입수량</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>박스환산수량</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>잔여수량</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>핸드폰번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>받는자주소</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>참고사항</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>주문기재사항</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>배송기재사항</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>세부참고사항</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>입력자</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>입력시간</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>수정자</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>수정시간</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>주문자명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>유효일자</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>온라인주문번호</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>의뢰일자</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>의뢰번호</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>박스수량</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>포장구분</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>WHCD</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>매핑명</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>의뢰구분</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>LOT</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>판매금액</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>옵션명</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>택배사</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
         </is>

--- a/중복출고_분석결과.xlsx
+++ b/중복출고_분석결과.xlsx
@@ -1469,10 +1469,14 @@
         <v>6</v>
       </c>
       <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1507,10 +1511,14 @@
         <v>3</v>
       </c>
       <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1545,10 +1553,14 @@
         <v>6</v>
       </c>
       <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
         <v>0</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1951,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2475,120 +2487,6 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ON008</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>부주문코드</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026030213385111</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026030256326261</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LBP240</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ON008</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>부주문코드</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026030447444731</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026030419576921</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LNF</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ON008</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>부주문코드</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026030587891821</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026030580855221</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LB160</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3409,7 +3307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV45"/>
+  <dimension ref="A1:AV39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9793,42 +9691,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ON008</t>
+          <t>ON034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026030213385111</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026030256326261</t>
-        </is>
-      </c>
+          <t>262602270002020</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LBP240</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
+          <t>라놀린크림 40g</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>이진우</t>
+          <t>동탄 1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9838,7 +9732,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>536478520896</t>
+          <t>536463012536</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -9853,17 +9747,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>92756</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -9878,54 +9772,42 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>010-5585-5153</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>010-5585-5153</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도 청주시 청원구 오창읍 2산단4로 60 (오창읍, 충북오창사랑으로부영7단지) 707동 2201호 </t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
+          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
@@ -9934,52 +9816,48 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>2026-03-03 11:07:15</t>
+          <t>2026-02-27 12:42:31</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>PC00</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-03-03 16:25:35</t>
+          <t>2026-03-04 10:15:11</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>이진우</t>
+          <t>티엘지</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>2027-08-05</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>2127711698</t>
-        </is>
-      </c>
+          <t>2028-08-01</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>00021</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>합포장</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -9987,26 +9865,22 @@
           <t>1001</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
-        </is>
-      </c>
+      <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>2022.08.05</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr"/>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>89700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>LBP240 란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함)단품</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -10023,42 +9897,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ON008</t>
+          <t>ON034</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026030213385111</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026030256326261</t>
-        </is>
-      </c>
+          <t>262602270002020</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LBP240</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
+          <t>라놀린크림 40g</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>이진우</t>
+          <t>동탄 11</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -10068,7 +9938,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>536478520896</t>
+          <t>536463012540</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -10083,17 +9953,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>92756</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -10108,7 +9978,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -10118,44 +9988,32 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>010-5585-5153</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>010-5585-5153</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t xml:space="preserve">충청북도 청주시 청원구 오창읍 2산단4로 60 (오창읍, 충북오창사랑으로부영7단지) 707동 2201호 </t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
+          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
@@ -10164,42 +10022,38 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>2026-03-03 11:07:15</t>
+          <t>2026-02-27 12:42:31</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>PC00</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-03-03 16:25:35</t>
+          <t>2026-03-04 10:15:11</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>이진우</t>
+          <t>티엘지</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>2027-08-05</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>2127711698</t>
-        </is>
-      </c>
+          <t>2028-08-01</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>00021</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -10209,7 +10063,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>합포장</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -10217,26 +10071,22 @@
           <t>1001</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
-        </is>
-      </c>
+      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>89700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>LBP240 란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함)단품</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -10253,37 +10103,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ON008</t>
+          <t>ON034</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026030447444731</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026030419576921</t>
-        </is>
-      </c>
+          <t>262602270002020</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LNF</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
+          <t>라놀린크림 40g</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>정연호</t>
+          <t>동탄 12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -10298,7 +10144,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>536487196044</t>
+          <t>536463012551</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -10313,17 +10159,17 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>90604</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -10338,7 +10184,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -10348,44 +10194,32 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>010-4696-0613</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>010-4696-0613</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>61620</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시 남구 월산로95번길 6 (월산동, 힐스테이트 월산) 103동 504호 </t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
+          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
@@ -10394,34 +10228,30 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>2026-03-04 10:33:58</t>
+          <t>2026-02-27 12:42:31</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>PC00</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-03-04 11:55:21</t>
+          <t>2026-03-04 10:15:11</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>정선옥</t>
+          <t>티엘지</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>2028-12-05</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>2127883536</t>
-        </is>
-      </c>
+          <t>2028-08-01</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -10429,7 +10259,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>00025</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -10439,7 +10269,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>합포장</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
@@ -10447,26 +10277,22 @@
           <t>1001</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
-        </is>
-      </c>
+      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>1014541</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr"/>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>LNF [SKU]란시노 젖병 젖꼭지 내추럴 웨이브 2개입_F(6~12)개월단품</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -10483,37 +10309,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ON008</t>
+          <t>ON034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026030447444731</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026030419576921</t>
-        </is>
-      </c>
+          <t>262602270002020</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LNF</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
+          <t>라놀린크림 40g</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>정연호</t>
+          <t>동탄 13</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10528,7 +10350,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>536487196044</t>
+          <t>536463012562</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -10543,17 +10365,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>90604</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -10568,7 +10390,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -10578,44 +10400,32 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>010-4696-0613</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>010-4696-0613</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>61620</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t xml:space="preserve">광주광역시 남구 월산로95번길 6 (월산동, 힐스테이트 월산) 103동 504호 </t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 일반 배송</t>
-        </is>
-      </c>
+          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
@@ -10624,34 +10434,30 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>2026-03-04 10:33:58</t>
+          <t>2026-02-27 12:42:31</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>PC00</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-03-04 11:55:21</t>
+          <t>2026-03-04 10:15:11</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>정선옥</t>
+          <t>티엘지</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>2028-12-06</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>2127883536</t>
-        </is>
-      </c>
+          <t>2028-08-01</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
@@ -10659,7 +10465,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>00025</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -10669,7 +10475,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>합포장</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -10677,26 +10483,22 @@
           <t>1001</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
-        </is>
-      </c>
+      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>1014541</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr"/>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>LNF [SKU]란시노 젖병 젖꼭지 내추럴 웨이브 2개입_F(6~12)개월단품</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -10713,42 +10515,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ON008</t>
+          <t>ON034</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026030587891821</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026030580855221</t>
-        </is>
-      </c>
+          <t>262602270002020</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LB160</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>란시노 내추럴웨이브 젖병 160ml S</t>
+          <t>라놀린크림 40g</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>최현정</t>
+          <t>동탄 14</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -10758,7 +10556,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>536501417620</t>
+          <t>536463012573</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -10773,17 +10571,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -10798,7 +10596,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -10808,44 +10606,32 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>010-4418-1217</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>010-4418-1217</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>01705</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시 노원구 노원로28길 62 (상계동, 한일유앤아이아파트) 104동 1402호 </t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 선물하기 일반 배송</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 선물하기 일반 배송</t>
-        </is>
-      </c>
+          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
@@ -10854,42 +10640,38 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>2026-03-06 14:25:08</t>
+          <t>2026-02-27 12:42:31</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>PC00</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-03-06 16:30:35</t>
+          <t>2026-03-04 10:15:11</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>김*안</t>
+          <t>티엘지</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>2030-04-07</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2128150608</t>
-        </is>
-      </c>
+          <t>2028-08-01</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>00040</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -10899,7 +10681,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>합포장</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
@@ -10907,26 +10689,22 @@
           <t>1001</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>란시노 내추럴웨이브 젖병 160ml S</t>
-        </is>
-      </c>
+      <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>20250408</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr"/>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>145800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>LB160 란시노 신생아 배앓이 유리젖병 160ml단품</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -10943,22 +10721,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ON008</t>
+          <t>ON034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026030587891821</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026030580855221</t>
-        </is>
-      </c>
+          <t>262602270002020</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LB160</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10968,17 +10742,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>란시노 내추럴웨이브 젖병 160ml S</t>
+          <t>라놀린크림 40g</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>최현정1</t>
+          <t>동탄 15</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -10988,7 +10762,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>536502250605</t>
+          <t>536463012584</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -11003,17 +10777,17 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>91149</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -11028,7 +10802,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -11043,39 +10817,27 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>010-4418-1217</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>010-4418-1217</t>
+          <t>070-7771-6872</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>01705</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t xml:space="preserve">서울특별시 노원구 노원로28길 62 (상계동, 한일유앤아이아파트) 104동 1402호 </t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 선물하기 일반 배송</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>택배, 등기, 소포 선물하기 일반 배송</t>
-        </is>
-      </c>
+          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
@@ -11084,42 +10846,38 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>2026-03-06 14:25:08</t>
+          <t>2026-02-27 12:42:31</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>PC00</t>
+          <t>SK01</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-03-06 16:30:37</t>
+          <t>2026-03-04 10:15:11</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>김*안</t>
+          <t>티엘지</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>2030-04-07</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>2128150608</t>
-        </is>
-      </c>
+          <t>2028-08-01</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>00040</t>
+          <t>00003</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -11129,7 +10887,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>합포장</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
@@ -11137,26 +10895,22 @@
           <t>1001</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>란시노 내추럴웨이브 젖병 160ml S</t>
-        </is>
-      </c>
+      <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>20250408</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>145800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>LB160 란시노 신생아 배앓이 유리젖병 160ml단품</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
@@ -11189,7 +10943,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11199,7 +10953,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>동탄 1</t>
+          <t>동탄 16</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11214,7 +10968,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>536463012536</t>
+          <t>536463012595</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -11259,7 +11013,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -11334,7 +11088,7 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -11379,38 +11133,38 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ON034</t>
+          <t>TLG008</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>262602270002020</t>
+          <t>26260305500110</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>라놀린크림 40g</t>
+          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>동탄 11</t>
+          <t>인천 32</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -11420,32 +11174,32 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>536463012540</t>
+          <t>536495923972</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ONR01</t>
+          <t>TLG01</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>아이디1</t>
+          <t>아이디2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>90047</t>
+          <t>91079</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -11460,12 +11214,12 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -11475,25 +11229,29 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>070-7771-6872</t>
+          <t>070-4747-2982</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>070-7771-6872</t>
+          <t>070-4747-2982</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
+          <t>인천광역시 서구 봉수대로 370 석남혁신물류센터 6층 B동 604 DOCK</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
@@ -11504,17 +11262,17 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>2026-02-27 12:42:31</t>
+          <t>2026-03-05 14:43:26</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>SK01</t>
+          <t>PC01</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-03-04 10:15:11</t>
+          <t>2026-03-06 09:14:16</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -11524,23 +11282,23 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>2028-08-01</t>
+          <t>2029-02-12</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>00003</t>
+          <t>00005</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -11557,7 +11315,7 @@
       <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>1014541</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr"/>
@@ -11568,7 +11326,7 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
@@ -11585,18 +11343,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ON034</t>
+          <t>TLG008</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>262602270002020</t>
+          <t>26260305500110</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11606,17 +11364,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>라놀린크림 40g</t>
+          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>동탄 12</t>
+          <t>인천 321</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -11626,32 +11384,32 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>536463012551</t>
+          <t>536495924020</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ONR01</t>
+          <t>TLG01</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>아이디1</t>
+          <t>아이디2</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>90047</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -11666,7 +11424,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -11681,25 +11439,29 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>070-7771-6872</t>
+          <t>070-4747-2982</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>070-7771-6872</t>
+          <t>070-4747-2982</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
+          <t>인천광역시 서구 봉수대로 370 석남혁신물류센터 6층 B동 604 DOCK</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
@@ -11710,17 +11472,17 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>2026-02-27 12:42:31</t>
+          <t>2026-03-05 14:43:26</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>SK01</t>
+          <t>PC01</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-03-04 10:15:11</t>
+          <t>2026-03-06 09:14:18</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
@@ -11730,18 +11492,18 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>2028-08-01</t>
+          <t>2029-02-12</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>00003</t>
+          <t>00005</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -11763,7 +11525,7 @@
       <c r="AP38" t="inlineStr"/>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>1014541</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr"/>
@@ -11774,7 +11536,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -11791,18 +11553,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ON034</t>
+          <t>TLG008</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>262602270002020</t>
+          <t>26260305500110</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -11812,17 +11574,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>라놀린크림 40g</t>
+          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>동탄 13</t>
+          <t>인천 322</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -11832,32 +11594,32 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>536463012562</t>
+          <t>536495924042</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ONR01</t>
+          <t>TLG01</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>아이디1</t>
+          <t>아이디2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>90047</t>
+          <t>91081</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -11872,7 +11634,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -11887,25 +11649,29 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>070-7771-6872</t>
+          <t>070-4747-2982</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>070-7771-6872</t>
+          <t>070-4747-2982</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
+          <t>인천광역시 서구 봉수대로 370 석남혁신물류센터 6층 B동 604 DOCK</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
@@ -11916,17 +11682,17 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>2026-02-27 12:42:31</t>
+          <t>2026-03-05 14:43:26</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>SK01</t>
+          <t>PC01</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-03-04 10:15:11</t>
+          <t>2026-03-06 09:14:19</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -11936,18 +11702,18 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>2028-08-01</t>
+          <t>2029-02-12</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>00003</t>
+          <t>00005</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
@@ -11969,7 +11735,7 @@
       <c r="AP39" t="inlineStr"/>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>1014541</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr"/>
@@ -11980,7 +11746,7 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
@@ -11989,1254 +11755,6 @@
         </is>
       </c>
       <c r="AV39" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ON034</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>262602270002020</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC040</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>라놀린크림 40g</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>동탄 14</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>536463012573</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>ONR01</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>아이디1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>90047</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>란시노</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>070-7771-6872</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>070-7771-6872</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>2026-02-27 12:42:31</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>2026-03-04 10:15:11</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>티엘지</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>2028-08-01</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>00003</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>23370</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr"/>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr">
-        <is>
-          <t>LC040</t>
-        </is>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>A00004</t>
-        </is>
-      </c>
-      <c r="AV40" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ON034</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>262602270002020</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC040</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>라놀린크림 40g</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>동탄 15</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>536463012584</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>ONR01</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>아이디1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>90047</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>란시노</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>070-7771-6872</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>070-7771-6872</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>2026-02-27 12:42:31</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>2026-03-04 10:15:11</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>티엘지</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>2028-08-01</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>00003</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>23370</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr">
-        <is>
-          <t>LC040</t>
-        </is>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>A00004</t>
-        </is>
-      </c>
-      <c r="AV41" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ON034</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>262602270002020</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC040</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>라놀린크림 40g</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>동탄 16</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>536463012595</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>ONR01</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>아이디1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>90047</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>란시노</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>070-7771-6872</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>070-7771-6872</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>경기도 화성시 동탄물류1로13 쿠팡동탄물류센터 3F 3번 Dock 로켓그로스 하차장</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>2026-02-27 12:42:31</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>2026-03-04 10:15:11</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>티엘지</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>2028-08-01</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>00003</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>23370</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr">
-        <is>
-          <t>LC040</t>
-        </is>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>A00004</t>
-        </is>
-      </c>
-      <c r="AV42" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TLG008</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>26260305500110</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LNF</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>인천 32</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>536495923972</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>TLG01</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>아이디2</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>91079</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>란시노</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>070-4747-2982</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>070-4747-2982</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>22788</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 봉수대로 370 석남혁신물류센터 6층 B동 604 DOCK</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>2026-03-05 14:43:26</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>PC01</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>2026-03-06 09:14:16</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>티엘지</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>2029-02-12</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>00005</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>1014541</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr"/>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr">
-        <is>
-          <t>LNF</t>
-        </is>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>A00004</t>
-        </is>
-      </c>
-      <c r="AV43" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TLG008</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>26260305500110</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LNF</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>인천 321</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>536495924020</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>TLG01</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>아이디2</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>91080</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>란시노</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>070-4747-2982</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>070-4747-2982</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>22788</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 봉수대로 370 석남혁신물류센터 6층 B동 604 DOCK</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>2026-03-05 14:43:26</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>PC01</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>2026-03-06 09:14:18</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>티엘지</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>2029-02-12</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>00005</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>1014541</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr">
-        <is>
-          <t>LNF</t>
-        </is>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>A00004</t>
-        </is>
-      </c>
-      <c r="AV44" t="inlineStr">
-        <is>
-          <t>상품</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TLG008</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>26260305500110</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>LNF</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>인천 322</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>536495924042</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>TLG01</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>아이디2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>91081</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>란시노</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>070-4747-2982</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>070-4747-2982</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>22788</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 봉수대로 370 석남혁신물류센터 6층 B동 604 DOCK</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>출고확정스캔</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>SK01</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>2026-03-05 14:43:26</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>PC01</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>2026-03-06 09:14:19</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>티엘지</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>2029-02-12</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>00005</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>1014541</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr">
-        <is>
-          <t>LNF</t>
-        </is>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>A00004</t>
-        </is>
-      </c>
-      <c r="AV45" t="inlineStr">
         <is>
           <t>상품</t>
         </is>
@@ -13253,7 +11771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13353,7 +11871,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ON003</t>
+          <t>ON008</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -13363,30 +11881,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20260303-0000012</t>
+          <t>2026030213385111</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20260303-0000012-01</t>
+          <t>2026030256326261</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LBP240</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -13405,30 +11923,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20260303-0000091</t>
+          <t>20260303-0000012</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20260303-0000091-04</t>
+          <t>20260303-0000012-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LB240</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -13447,30 +11965,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20260303-0000507</t>
+          <t>20260303-0000091</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20260303-0000507-01</t>
+          <t>20260303-0000091-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LB240</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -13489,12 +12007,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20260303-0001713</t>
+          <t>20260303-0000507</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20260303-0001713-01</t>
+          <t>20260303-0000507-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -13531,30 +12049,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20260304-0000021</t>
+          <t>20260303-0001713</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20260304-0000021-04</t>
+          <t>20260303-0001713-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LNF</t>
+          <t>LC040</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -13573,30 +12091,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20260304-0000036</t>
+          <t>20260304-0000021</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20260304-0000036-02</t>
+          <t>20260304-0000021-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LB160</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -13615,12 +12133,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20260304-0000068</t>
+          <t>20260304-0000036</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20260304-0000068-01</t>
+          <t>20260304-0000036-02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -13629,16 +12147,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -13657,12 +12175,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20260304-0000093</t>
+          <t>20260304-0000068</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20260304-0000093-05</t>
+          <t>20260304-0000068-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -13671,16 +12189,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -13699,12 +12217,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20260304-0001478</t>
+          <t>20260304-0000093</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20260304-0001478-02</t>
+          <t>20260304-0000093-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -13713,16 +12231,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -13741,30 +12259,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20260305-0000730</t>
+          <t>20260304-0001478</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20260305-0000730-01</t>
+          <t>20260304-0001478-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LB240</t>
+          <t>LB160</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -13773,7 +12291,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ON003</t>
+          <t>ON008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13783,32 +12301,158 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20260306-0001919</t>
+          <t>2026030447444731</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20260306-0001919-02</t>
+          <t>2026030419576921</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LC040</t>
+          <t>LNF</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ON003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>부주문코드</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20260305-0000730</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>20260305-0000730-01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LB240</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="b">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="I14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ON008</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>부주문코드</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026030587891821</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026030580855221</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LB160</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ON003</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>부주문코드</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20260306-0001919</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20260306-0001919-02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LC040</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13823,7 +12467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV30"/>
+  <dimension ref="A1:AV36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20597,6 +19241,1386 @@
         </is>
       </c>
       <c r="AV30" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ON008</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026030213385111</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026030256326261</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LBP240</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>이진우</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>536478520896</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ONR01</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>아이디1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>92756</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>란시노</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>010-5585-5153</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>010-5585-5153</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>28109</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충청북도 청주시 청원구 오창읍 2산단4로 60 (오창읍, 충북오창사랑으로부영7단지) 707동 2201호 </t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:07:15</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>PC00</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>2026-03-03 16:25:35</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>이진우</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>2027-08-05</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>2127711698</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>00021</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>합포장</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>2022.08.05</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>89700</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>LBP240 란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함)단품</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>A00004</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ON008</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026030213385111</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026030256326261</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LBP240</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>이진우</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>536478520896</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ONR01</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>아이디1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>92756</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>란시노</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>010-5585-5153</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>010-5585-5153</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>28109</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충청북도 청주시 청원구 오창읍 2산단4로 60 (오창읍, 충북오창사랑으로부영7단지) 707동 2201호 </t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:07:15</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>PC00</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>2026-03-03 16:25:35</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>이진우</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>2027-08-05</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>2127711698</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>00021</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>합포장</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함) 화이트 + 보라색 1개 240ml</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>75840</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>89700</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>LBP240 란시노 PP젖병 240ml 신생아 아기(젖꼭지M 포함)단품</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>A00004</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ON008</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026030447444731</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026030419576921</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LNF</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>정연호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>536487196044</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ONR01</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>아이디1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>90604</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>란시노</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>010-4696-0613</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>010-4696-0613</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>61620</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">광주광역시 남구 월산로95번길 6 (월산동, 힐스테이트 월산) 103동 504호 </t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:33:58</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>PC00</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:55:21</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>정선옥</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>2028-12-05</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>2127883536</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>00025</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>합포장</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>1014541</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>26700</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>LNF [SKU]란시노 젖병 젖꼭지 내추럴 웨이브 2개입_F(6~12)개월단품</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>A00004</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ON008</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026030447444731</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026030419576921</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LNF</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>정연호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>536487196044</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ONR01</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>아이디1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>90604</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>란시노</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>010-4696-0613</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>010-4696-0613</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>61620</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">광주광역시 남구 월산로95번길 6 (월산동, 힐스테이트 월산) 103동 504호 </t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 일반 배송</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:33:58</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>PC00</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>2026-03-04 11:55:21</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>정선옥</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>2028-12-06</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>2127883536</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>00025</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>합포장</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>란시노 내추럴 웨이브 젖꼭지, F(6~12개월), 2개</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>1014541</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>26700</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>LNF [SKU]란시노 젖병 젖꼭지 내추럴 웨이브 2개입_F(6~12)개월단품</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>A00004</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ON008</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026030587891821</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026030580855221</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LB160</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>란시노 내추럴웨이브 젖병 160ml S</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>최현정</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>536501417620</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ONR01</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>아이디1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>91148</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>란시노</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>010-4418-1217</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>010-4418-1217</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>01705</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시 노원구 노원로28길 62 (상계동, 한일유앤아이아파트) 104동 1402호 </t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 선물하기 일반 배송</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 선물하기 일반 배송</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:25:08</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>PC00</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>2026-03-06 16:30:35</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>김*안</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>2030-04-07</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>2128150608</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>00040</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>합포장</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>란시노 내추럴웨이브 젖병 160ml S</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>20250408</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>145800</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>LB160 란시노 신생아 배앓이 유리젖병 160ml단품</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>A00004</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ON008</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026030587891821</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026030580855221</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LB160</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>란시노 내추럴웨이브 젖병 160ml S</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>최현정1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>536502250605</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ONR01</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>아이디1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>91149</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>란시노</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>010-4418-1217</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>010-4418-1217</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>01705</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서울특별시 노원구 노원로28길 62 (상계동, 한일유앤아이아파트) 104동 1402호 </t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>출고확정스캔</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 선물하기 일반 배송</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>택배, 등기, 소포 선물하기 일반 배송</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>SK01</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>2026-03-06 14:25:08</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>PC00</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>2026-03-06 16:30:37</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>김*안</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>2030-04-07</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>2128150608</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>00040</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>합포장</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>란시노 내추럴웨이브 젖병 160ml S</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>20250408</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>145800</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>LB160 란시노 신생아 배앓이 유리젖병 160ml단품</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>A00004</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
         <is>
           <t>상품</t>
         </is>

--- a/중복출고_분석결과.xlsx
+++ b/중복출고_분석결과.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="★과잉출고_상세행" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cigro없음_요약" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cigro없음_상세행" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수량일치_중복_요약" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수량일치_중복_상세행" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정상_분할출고_요약" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="정상_분할출고_상세행" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
